--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_MFH_until_2004_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_MFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>15.66055972553271</v>
+        <v>23.5860184321467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>6882.50174270414</v>
       </c>
       <c r="F2" t="n">
-        <v>15.57855291193841</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="G2" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="H2" t="n">
-        <v>15.85832483874669</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="I2" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="J2" t="n">
-        <v>15.44523764224473</v>
+        <v>22.49563233093422</v>
       </c>
       <c r="K2" t="n">
         <v>6882.50174270414</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>15.66055972553271</v>
+        <v>23.5860184321467</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>6882.50174270414</v>
       </c>
       <c r="F3" t="n">
-        <v>15.57855291193841</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="G3" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="H3" t="n">
-        <v>15.85832483874669</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="I3" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="J3" t="n">
-        <v>15.44523764224473</v>
+        <v>22.49563233093422</v>
       </c>
       <c r="K3" t="n">
         <v>6882.50174270414</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>15.66055972553271</v>
+        <v>23.5860184321467</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>6882.50174270414</v>
       </c>
       <c r="F4" t="n">
-        <v>15.57855291193841</v>
+        <v>23.08036906184737</v>
       </c>
       <c r="G4" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="H4" t="n">
-        <v>15.85832483874669</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="I4" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="J4" t="n">
-        <v>15.44523764224473</v>
+        <v>22.49563233093422</v>
       </c>
       <c r="K4" t="n">
         <v>6882.50174270414</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>16.2328308487091</v>
+        <v>23.5860184321467</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>6882.50174270414</v>
       </c>
       <c r="F5" t="n">
-        <v>16.71495244072786</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="G5" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="H5" t="n">
-        <v>17.66514006402923</v>
+        <v>23.08036906184738</v>
       </c>
       <c r="I5" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="J5" t="n">
-        <v>17.54792988342766</v>
+        <v>22.49563233093422</v>
       </c>
       <c r="K5" t="n">
         <v>6882.50174270414</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>17.1603260530771</v>
+        <v>27.78634805404925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>6882.50174270414</v>
       </c>
       <c r="F6" t="n">
-        <v>17.44395016</v>
+        <v>25.52559580672949</v>
       </c>
       <c r="G6" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="H6" t="n">
-        <v>18.51348831460539</v>
+        <v>23.39095283809758</v>
       </c>
       <c r="I6" t="n">
         <v>6882.50174270414</v>
       </c>
       <c r="J6" t="n">
-        <v>18.51348831460539</v>
+        <v>23.83634281615042</v>
       </c>
       <c r="K6" t="n">
         <v>6882.50174270414</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5.507489344942785</v>
+        <v>5.953008316023738</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.507489344942785</v>
+        <v>5.953008316023738</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>7.242528848634551</v>
+        <v>7.828400885523859</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7.242528848634551</v>
+        <v>7.828400885523859</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>8.047152788634408</v>
+        <v>8.698113508842731</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8.047152788634408</v>
+        <v>8.698113508842731</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8.501135729835143</v>
+        <v>9.188820626920501</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8.501135729835143</v>
+        <v>9.188820626920501</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>10.32375261405621</v>
+        <v>11.158875</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>8.790429695536188</v>
+        <v>9.501516535297551</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>8.790429695536188</v>
+        <v>9.501516535297551</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001959462064921029</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001959462064921029</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001959462064921029</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001962372640808997</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.002025226411764706</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002025226411764706</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001944217355294118</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001962372640808997</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002025226411764706</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002025226411764706</v>
+        <v>0.001782199242352941</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02582163674999999</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.2892023316</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02582163675000004</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="G17" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02420188635214067</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="I17" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02582163675000004</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="K17" t="n">
         <v>0.2892023316</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02582163674999999</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.2892023316</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02582163675000004</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="G18" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02420188635214067</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="I18" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02582163675000004</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="K18" t="n">
         <v>0.2892023316</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02582163674999999</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.2892023316</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02599151300588389</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="G19" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="H19" t="n">
-        <v>0.02420188635214067</v>
+        <v>0.04415573965642281</v>
       </c>
       <c r="I19" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02582163675000004</v>
+        <v>0.0452078232753998</v>
       </c>
       <c r="K19" t="n">
         <v>0.2892023316</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02582163674999999</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.2892023316</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02389263766404401</v>
+        <v>0.04652278914483775</v>
       </c>
       <c r="G20" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01721442450000003</v>
+        <v>0.04415573965642279</v>
       </c>
       <c r="I20" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01721442450000003</v>
+        <v>0.04711795449545064</v>
       </c>
       <c r="K20" t="n">
         <v>0.2892023316</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02582163674999999</v>
+        <v>0.04303606125000002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.2892023316</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02389263766404401</v>
+        <v>0.05552069968573441</v>
       </c>
       <c r="G21" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01721442450000003</v>
+        <v>0.05736744100374883</v>
       </c>
       <c r="I21" t="n">
         <v>0.2892023316</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01721442450000003</v>
+        <v>0.05551406540257726</v>
       </c>
       <c r="K21" t="n">
         <v>0.2892023316</v>
@@ -2142,13 +2142,13 @@
         <v>4.814398697721012</v>
       </c>
       <c r="H46" t="n">
-        <v>3.77647620809301</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>3.716310206487722</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3.77647620809301</v>
       </c>
       <c r="K46" t="n">
         <v>3.716310206487722</v>
@@ -2159,7 +2159,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1930116371490517</v>
+        <v>0.1365576267347968</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2173,19 +2173,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2151041506824221</v>
+        <v>0.1414456714868868</v>
       </c>
       <c r="G47" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2781213062343181</v>
+        <v>0.1394798536892438</v>
       </c>
       <c r="I47" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2538820039380211</v>
+        <v>0.1446582868562795</v>
       </c>
       <c r="K47" t="n">
         <v>1.696537021532292</v>
@@ -2196,7 +2196,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1930116371490517</v>
+        <v>0.1365576267347968</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2210,19 +2210,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2151041506824221</v>
+        <v>0.1414456714868868</v>
       </c>
       <c r="G48" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2781213062343181</v>
+        <v>0.1394798536892438</v>
       </c>
       <c r="I48" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2538820039380211</v>
+        <v>0.1446582868562795</v>
       </c>
       <c r="K48" t="n">
         <v>1.696537021532292</v>
@@ -2233,7 +2233,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1930116371490517</v>
+        <v>0.1365576267347968</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2247,19 +2247,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2151041506824221</v>
+        <v>0.1414456714868868</v>
       </c>
       <c r="G49" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2781213062343181</v>
+        <v>0.1394798536892438</v>
       </c>
       <c r="I49" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2538820039380211</v>
+        <v>0.1446582868562795</v>
       </c>
       <c r="K49" t="n">
         <v>1.696537021532292</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.5808056375362783</v>
+        <v>0.6175212324694015</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4809916303851384</v>
+        <v>0.5031612216980822</v>
       </c>
       <c r="G52" t="n">
         <v>1.696537021532292</v>
@@ -2370,7 +2370,7 @@
         <v>0.4891366106906731</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5982593823727242</v>
+        <v>0.480061636365492</v>
       </c>
       <c r="K52" t="n">
         <v>0.4891366106906731</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5808056375362783</v>
+        <v>0.6175212324694015</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4809916303851384</v>
+        <v>0.5031612216980822</v>
       </c>
       <c r="G53" t="n">
         <v>1.696537021532292</v>
@@ -2407,7 +2407,7 @@
         <v>0.7073821540547753</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5982593823727242</v>
+        <v>0.480061636365492</v>
       </c>
       <c r="K53" t="n">
         <v>0.7073821540547753</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.5808056375362783</v>
+        <v>0.6175212324694015</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4809916303851384</v>
+        <v>0.5031612216980822</v>
       </c>
       <c r="G54" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6123517723811817</v>
+        <v>0.5982593823727242</v>
       </c>
       <c r="I54" t="n">
         <v>0.8260452714221604</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5983719402445957</v>
+        <v>0.480061636365492</v>
       </c>
       <c r="K54" t="n">
         <v>0.8260452714221604</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.7138993020066097</v>
+        <v>0.6802467425590077</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6750000749585143</v>
+        <v>0.6630736230953275</v>
       </c>
       <c r="G55" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6731790911791672</v>
+        <v>0.6659008249708938</v>
       </c>
       <c r="I55" t="n">
         <v>0.8990914851413956</v>
       </c>
       <c r="J55" t="n">
-        <v>0.70464496872474</v>
+        <v>0.6616687582712283</v>
       </c>
       <c r="K55" t="n">
         <v>0.8990914851413956</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7266522314365286</v>
+        <v>0.6811122676320176</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6750000749585143</v>
+        <v>0.6630736230953275</v>
       </c>
       <c r="G56" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6731790911791672</v>
+        <v>0.6659008249708938</v>
       </c>
       <c r="I56" t="n">
         <v>0.948144517556026</v>
       </c>
       <c r="J56" t="n">
-        <v>0.7057175969702724</v>
+        <v>0.6616687582712282</v>
       </c>
       <c r="K56" t="n">
         <v>0.948144517556026</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3201013248174135</v>
+        <v>0.08345996708398383</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3190675261003354</v>
+        <v>0.1068308280743862</v>
       </c>
       <c r="G62" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3175226343032741</v>
+        <v>0.08645838123088724</v>
       </c>
       <c r="I62" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3198036888344685</v>
+        <v>0.1057237717195686</v>
       </c>
       <c r="K62" t="n">
         <v>1.696537021532292</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3201013248174135</v>
+        <v>0.08345996708398383</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3190675261003354</v>
+        <v>0.1068308280743862</v>
       </c>
       <c r="G63" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3175226343032741</v>
+        <v>0.08645838123088724</v>
       </c>
       <c r="I63" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3198036888344685</v>
+        <v>0.1057237717195686</v>
       </c>
       <c r="K63" t="n">
         <v>1.696537021532292</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.3201013248174135</v>
+        <v>0.08345996708398383</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3190675261003354</v>
+        <v>0.1068308280743862</v>
       </c>
       <c r="G64" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3175226343032741</v>
+        <v>0.08645838123088724</v>
       </c>
       <c r="I64" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3198036888344685</v>
+        <v>0.1057237717195686</v>
       </c>
       <c r="K64" t="n">
         <v>1.696537021532292</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.3871280556597213</v>
+        <v>0.1187132878571642</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F65" t="n">
-        <v>0.423767337745229</v>
+        <v>0.1371938101204591</v>
       </c>
       <c r="G65" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4211343170403508</v>
+        <v>0.1335036260293754</v>
       </c>
       <c r="I65" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3902178622163476</v>
+        <v>0.1389479490136682</v>
       </c>
       <c r="K65" t="n">
         <v>1.696537021532292</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4010062089857775</v>
+        <v>0.1353869226916388</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4513288774625908</v>
+        <v>0.1678650657204936</v>
       </c>
       <c r="G66" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4481364011422252</v>
+        <v>0.1777774258242334</v>
       </c>
       <c r="I66" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4155978953511199</v>
+        <v>0.1791935172680292</v>
       </c>
       <c r="K66" t="n">
         <v>1.696537021532292</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.03708792462925819</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J72" t="n">
-        <v>0.02389459399870552</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.03708792462925819</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.06463666724067875</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J73" t="n">
-        <v>0.02389459399870552</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.06463666724067875</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0874419385652509</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02389459399870552</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.0874419385652509</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1069596343813798</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1069596343813798</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1239587199090238</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1239587199090238</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="77">
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1517740433107318</v>
+        <v>0.1128664690700577</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3283,22 +3283,22 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2309137425843027</v>
+        <v>0.2019659882457879</v>
       </c>
       <c r="G77" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H77" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.1292060922122877</v>
       </c>
       <c r="I77" t="n">
-        <v>0.03708792462925819</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.2271651752380603</v>
       </c>
       <c r="K77" t="n">
-        <v>0.03708792462925819</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1517740433107318</v>
+        <v>0.1128664690700577</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3320,22 +3320,22 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2309137425843027</v>
+        <v>0.2019659882457879</v>
       </c>
       <c r="G78" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H78" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.1292060922122877</v>
       </c>
       <c r="I78" t="n">
-        <v>0.06463666724067875</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J78" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.2271651752380603</v>
       </c>
       <c r="K78" t="n">
-        <v>0.06463666724067875</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1517740433107318</v>
+        <v>0.1128664690700577</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3357,22 +3357,22 @@
         <v>1.696537021532292</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2309137425843027</v>
+        <v>0.2019659882457879</v>
       </c>
       <c r="G79" t="n">
         <v>1.696537021532292</v>
       </c>
       <c r="H79" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.1292060922122877</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0874419385652509</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J79" t="n">
-        <v>0.05086229593496847</v>
+        <v>0.2271651752380603</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0874419385652509</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1069596343813798</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1069596343813798</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1239587199090238</v>
+        <v>1.696537021532292</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1239587199090238</v>
+        <v>1.696537021532292</v>
       </c>
     </row>
     <row r="82">
